--- a/webscrapping/sofascore/Server/files_initted/jugadores_info_db.xlsx
+++ b/webscrapping/sofascore/Server/files_initted/jugadores_info_db.xlsx
@@ -7142,7 +7142,7 @@
         <v>754</v>
       </c>
       <c r="C123">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D123" t="s">
         <v>1251</v>

--- a/webscrapping/sofascore/Server/files_initted/jugadores_info_db.xlsx
+++ b/webscrapping/sofascore/Server/files_initted/jugadores_info_db.xlsx
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D92" t="n">
         <v>1100000</v>
@@ -13028,7 +13028,7 @@
         </is>
       </c>
       <c r="C371" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D371" t="n">
         <v>850000</v>
@@ -18910,7 +18910,7 @@
         </is>
       </c>
       <c r="C544" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D544" t="n">
         <v>12800000</v>

--- a/webscrapping/sofascore/Server/files_initted/jugadores_info_db.xlsx
+++ b/webscrapping/sofascore/Server/files_initted/jugadores_info_db.xlsx
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" t="n">
         <v>1400000</v>
@@ -11566,7 +11566,7 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D328" t="n">
         <v>38000000</v>

--- a/webscrapping/sofascore/Server/files_initted/jugadores_info_db.xlsx
+++ b/webscrapping/sofascore/Server/files_initted/jugadores_info_db.xlsx
@@ -13087,7 +13087,7 @@
         <v>843</v>
       </c>
       <c r="C376">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D376">
         <v>1700000</v>
